--- a/Memorial/base_de_dados_memorial.xlsx
+++ b/Memorial/base_de_dados_memorial.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SITE\Memorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B2CBAF-76A5-4453-931B-D962D741F51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36752E2C-66F9-4CBB-B72D-27D6BE237A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{62DDFE69-0938-486F-9E38-C3C7E88D8C56}"/>
   </bookViews>
@@ -44,7 +44,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="2">
+  <futureMetadata name="XLRICHVALUE" count="3">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -59,20 +59,30 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="2">
+  <valueMetadata count="3">
     <bk>
       <rc t="1" v="0"/>
     </bk>
     <bk>
       <rc t="1" v="1"/>
     </bk>
+    <bk>
+      <rc t="1" v="2"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>As tomadas deverão ter corpo em plástico e todos os elementos da pinagem deverão estar devidamente protegidos (não expostos). 
 Todas as tomadas deverão seguir o padrão brasileiro, 2P+T, segundo a norma ABNT NBR 14136, corrente nominal e cores conforme legenda em projeto. 
@@ -99,6 +109,19 @@
   </si>
   <si>
     <t>Tomada Sobrepor Metélica</t>
+  </si>
+  <si>
+    <t>Imagem Ilustrativa de uma tomada de sobrepor metálica</t>
+  </si>
+  <si>
+    <t>Tomada Sobrepor 3P+T</t>
+  </si>
+  <si>
+    <t>As tomadas de sobrepor 3P+T deverão ser próprias para instalação aparente, com corrente nominal, tensão e grau de proteção compatíveis com a carga atendida e conforme indicado em projeto. Deverão possuir bornes adequados para conexão das fases e do condutor de proteção, garantindo fixação segura, proteção contra partes energizadas expostas e atendimento às normas técnicas aplicáveis.
+A instalação deverá ser executada em caixa ou invólucro apropriado, devidamente fixado à superfície, interligado à infraestrutura elétrica prevista e conectado ao sistema de aterramento da edificação por meio de condutor de proteção.</t>
+  </si>
+  <si>
+    <t>Imagem Ilustrativa de uma tomada de 3P+T</t>
   </si>
 </sst>
 </file>
@@ -134,7 +157,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -144,9 +167,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -209,7 +229,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -218,6 +238,10 @@
     <v>1</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>2</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -234,6 +258,7 @@
 <richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
+  <rel r:id="rId3"/>
 </richValueRels>
 </file>
 
@@ -554,20 +579,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{567322C1-B302-483D-95DA-3FC165D43CCF}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="95.21875" style="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="2" customWidth="1"/>
-    <col min="4" max="4" width="41.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -587,7 +612,7 @@
       <c r="C2" s="2" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -601,8 +626,22 @@
       <c r="C3" s="2" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>4</v>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Memorial/base_de_dados_memorial.xlsx
+++ b/Memorial/base_de_dados_memorial.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SITE\Memorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36752E2C-66F9-4CBB-B72D-27D6BE237A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A635B8-C3D7-4458-BA92-61BEEC70E64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" xr2:uid="{62DDFE69-0938-486F-9E38-C3C7E88D8C56}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{62DDFE69-0938-486F-9E38-C3C7E88D8C56}"/>
   </bookViews>
   <sheets>
     <sheet name="tomada" sheetId="1" r:id="rId1"/>
-    <sheet name="luminária" sheetId="2" r:id="rId2"/>
+    <sheet name="eletrocalha" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +44,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="6">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -66,8 +66,29 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="3"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="4"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="6">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -76,13 +97,22 @@
     </bk>
     <bk>
       <rc t="1" v="2"/>
+    </bk>
+    <bk>
+      <rc t="1" v="3"/>
+    </bk>
+    <bk>
+      <rc t="1" v="4"/>
+    </bk>
+    <bk>
+      <rc t="1" v="5"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t>As tomadas deverão ter corpo em plástico e todos os elementos da pinagem deverão estar devidamente protegidos (não expostos). 
 Todas as tomadas deverão seguir o padrão brasileiro, 2P+T, segundo a norma ABNT NBR 14136, corrente nominal e cores conforme legenda em projeto. 
@@ -122,6 +152,36 @@
   </si>
   <si>
     <t>Imagem Ilustrativa de uma tomada de 3P+T</t>
+  </si>
+  <si>
+    <t>Eletrocalha Lisa</t>
+  </si>
+  <si>
+    <t>Para a passagem dos condutores de energia que alimentam os diversos pontos da edificação, deverão ser utilizadas eletrocalhas lisas com virola de ferro, galvanizadas a fogo, chapa mínima #18USG.
+A sustentação das eletrocalhas será por meio de suporte horizontal para eletrocalha, atirantado à laje de teto por meio de vergalhão com rosca total. Este suporte deverá ser instalado a cada 1,5m.</t>
+  </si>
+  <si>
+    <t>Imagem Ilustrativa de uma Eletrocalha Perfurada</t>
+  </si>
+  <si>
+    <t>Imagem Ilustrativa de uma Eletrocalha Lisa</t>
+  </si>
+  <si>
+    <t>Para a passagem dos condutores de energia que alimentam os diversos pontos da edificação, deverão ser utilizadas eletrocalhas perfuradas sem virola de ferro, galvanizadas a fogo, chapa mínima #18USG. A sustentação das eletrocalhas será por meio de suporte horizontal para eletrocalha, atirantado à laje de teto por meio de vergalhão com rosca total. Este suporte deverá ser instalado a cada 1,5m.</t>
+  </si>
+  <si>
+    <t>Eletrocalha Perfurada</t>
+  </si>
+  <si>
+    <t>Para a passagem dos condutores de energia que alimentam os diversos pontos da edificação, deverão ser utilizadas eletrocalhas aramadas metálicas, galvanizadas, com dimensões conforme indicado em projeto e capacidade adequada à quantidade de condutores instalados.
+As eletrocalhas aramadas deverão ser instaladas sobre o solo, em trajeto definido em projeto, devidamente apoiadas, niveladas e organizadas, garantindo estabilidade mecânica, proteção dos condutores e facilidade de inspeção e manutenção. Deverão ser utilizados acessórios compatíveis, tais como curvas, emendas, derivações, suportes e fixadores, de forma a assegurar a continuidade e o correto alinhamento da infraestrutura.
+A instalação deverá evitar pontos de esmagamento, arestas cortantes, obstruções ou interferências com outros sistemas da edificação. Quando necessário, deverão ser previstas proteções adicionais contra impactos mecânicos, umidade ou contato direto com áreas sujeitas à circulação e movimentação de materiais.</t>
+  </si>
+  <si>
+    <t>Eletrocalha Aramada</t>
+  </si>
+  <si>
+    <t>Imagem Ilustrativa de uma Eletrocalha Aramada</t>
   </si>
 </sst>
 </file>
@@ -157,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -170,6 +230,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -229,7 +292,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -242,6 +305,18 @@
     <v>2</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>3</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>4</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>5</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -259,6 +334,9 @@
   <rel r:id="rId1"/>
   <rel r:id="rId2"/>
   <rel r:id="rId3"/>
+  <rel r:id="rId4"/>
+  <rel r:id="rId5"/>
+  <rel r:id="rId6"/>
 </richValueRels>
 </file>
 
@@ -651,9 +729,72 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97391718-DDDA-4479-BEF7-616E103DA4A2}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.21875" customWidth="1"/>
+    <col min="3" max="3" width="11" style="5" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="5" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="177.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Memorial/base_de_dados_memorial.xlsx
+++ b/Memorial/base_de_dados_memorial.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SITE\Memorial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1A635B8-C3D7-4458-BA92-61BEEC70E64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{209A6B5F-711D-4580-B528-DF877F3C6B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{62DDFE69-0938-486F-9E38-C3C7E88D8C56}"/>
+    <workbookView xWindow="28680" yWindow="45" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{62DDFE69-0938-486F-9E38-C3C7E88D8C56}"/>
   </bookViews>
   <sheets>
     <sheet name="tomada" sheetId="1" r:id="rId1"/>
     <sheet name="eletrocalha" sheetId="2" r:id="rId2"/>
+    <sheet name="iluminacao" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="6">
+  <futureMetadata name="XLRICHVALUE" count="8">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -87,8 +88,22 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="6"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="7"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="6">
+  <valueMetadata count="8">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -106,13 +121,19 @@
     </bk>
     <bk>
       <rc t="1" v="5"/>
+    </bk>
+    <bk>
+      <rc t="1" v="6"/>
+    </bk>
+    <bk>
+      <rc t="1" v="7"/>
     </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>As tomadas deverão ter corpo em plástico e todos os elementos da pinagem deverão estar devidamente protegidos (não expostos). 
 Todas as tomadas deverão seguir o padrão brasileiro, 2P+T, segundo a norma ABNT NBR 14136, corrente nominal e cores conforme legenda em projeto. 
@@ -182,6 +203,27 @@
   </si>
   <si>
     <t>Imagem Ilustrativa de uma Eletrocalha Aramada</t>
+  </si>
+  <si>
+    <t>Cabo PP</t>
+  </si>
+  <si>
+    <t>A ligação das luminárias deverá ser realizada por meio de cabo PP tripolar, composto por condutores de fase, neutro e proteção, com seção compatível com a carga instalada e conforme indicado em projeto.
+Cada luminária deverá possuir conexão por meio de conjunto plugue macho e plugue fêmea, permitindo a interligação entre a infraestrutura elétrica e o equipamento de iluminação de forma segura, prática e removível. Os conectores deverão ser compatíveis com a tensão e corrente do circuito, garantindo firmeza na conexão, isolamento adequado das partes energizadas e facilidade de manutenção ou substituição das luminárias.
+O condutor de proteção deverá ser devidamente conectado à carcaça metálica da luminária, quando aplicável, assegurando a continuidade do aterramento e a segurança da instalação.</t>
+  </si>
+  <si>
+    <t>Imagem Ilustrativa de um cabo tripolar com plugue fêmea</t>
+  </si>
+  <si>
+    <t>A ligação das luminárias deverá ser realizada com condutores de cobre isolados, com seção de 1,5 mm² ou 2,5 mm², conforme dimensionamento e indicação específica do projeto elétrico. Os condutores deverão contemplar fase, neutro e proteção, quando aplicável, garantindo a correta alimentação e segurança do ponto de iluminação.
+A conexão entre os condutores do circuito e os terminais das luminárias deverá ser executada por meio de conectores de emenda tipo Wago ou equivalente técnico, compatíveis com a seção dos cabos e com a corrente do circuito. As conexões deverão assegurar firmeza mecânica, continuidade elétrica, isolamento adequado e facilidade de manutenção ou substituição das luminárias.</t>
+  </si>
+  <si>
+    <t>Conector tipo wago</t>
+  </si>
+  <si>
+    <t>Imagem Ilustrativa de um conector tipo wago</t>
   </si>
 </sst>
 </file>
@@ -292,7 +334,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -317,6 +359,14 @@
     <v>5</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>6</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>7</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -337,6 +387,8 @@
   <rel r:id="rId4"/>
   <rel r:id="rId5"/>
   <rel r:id="rId6"/>
+  <rel r:id="rId7"/>
+  <rel r:id="rId8"/>
 </richValueRels>
 </file>
 
@@ -797,4 +849,62 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCE01261-5E36-4D59-9F48-178B0C60A6A6}">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.21875" customWidth="1"/>
+    <col min="3" max="3" width="11" style="3" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="131.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="3" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>